--- a/output/pdf_financials_xlsx/QST.xlsx
+++ b/output/pdf_financials_xlsx/QST.xlsx
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.708398</v>
+        <v>-4.121336</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.140672</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.914867</v>
+        <v>-2.914867</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.018148</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.914867</v>
+        <v>-2.914867</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.018148</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.708398</v>
+        <v>-4.121336</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.140672</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.711845</v>
+        <v>-4.117889</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.144292</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>13.78864078812439</v>
+        <v>-33.16894475047027</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>1.778547360239164</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>70.61990238808521</v>
+        <v>-29.27373550712681</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>112.90093266606</v>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>23.47879276929733</v>
+        <v>-23.47879276929733</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-0.2236927722508549</v>
@@ -6506,25 +6506,25 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.6222259999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.676834</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.703156</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.875288</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.108074</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.163705</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.39501</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>1.702303</v>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="H99" s="3" t="n">
-        <v>2.914867</v>
+        <v>-2.914867</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-0.018148</v>
@@ -17678,7 +17678,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -18822,7 +18826,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -19534,7 +19542,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -21008,7 +21020,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -23114,7 +23130,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -83098,7 +83118,7 @@
         </is>
       </c>
       <c r="K706" s="5" t="n">
-        <v>2.914867</v>
+        <v>-2.914867</v>
       </c>
       <c r="L706" s="5" t="n">
         <v>-0.018148</v>

--- a/output/pdf_financials_xlsx/QST.xlsx
+++ b/output/pdf_financials_xlsx/QST.xlsx
@@ -2776,19 +2776,19 @@
         <v>5.64057</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5.127371</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.733897</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.847863</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>8.809644</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>13.491383</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>16.307029</v>
@@ -2902,19 +2902,19 @@
         <v>5.64057</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>5.127371</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.733897</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.847863</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>8.809644</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>13.491383</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>16.307029</v>
@@ -3658,19 +3658,19 @@
         <v>0.168865</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.902102</v>
+        <v>0.7747309999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.431163</v>
+        <v>0.6972660000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.934489</v>
+        <v>1.086626</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.722383</v>
+        <v>1.912739</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>14.764655</v>
+        <v>1.273272</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.505262</v>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -87726,7 +87726,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E750" s="5" t="n">
@@ -88154,7 +88154,7 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E754" s="5" t="n">

--- a/output/pdf_financials_xlsx/QST.xlsx
+++ b/output/pdf_financials_xlsx/QST.xlsx
@@ -2366,25 +2366,25 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.001218</v>
+        <v>0.03256</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.001218</v>
+        <v>0.042534</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.001218</v>
+        <v>0.042479</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.003447</v>
+        <v>0.048294</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.00362</v>
+        <v>0.047934</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.003621</v>
+        <v>0.045959</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.358211</v>
+        <v>0.393859</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0.230062</v>
@@ -2396,13 +2396,13 @@
         <v>0.286609</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>2.469026</v>
+        <v>0.269442</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.422832</v>
+        <v>0.140125</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>2.277394</v>
+        <v>0.236826</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0.002077</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.117889</v>
+        <v>-4.073042</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.144292</v>
+        <v>0.188606</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>5.968623</v>
+        <v>6.004271</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>10.220112</v>
@@ -2467,7 +2467,7 @@
         <v>-1.543267</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.519359</v>
+        <v>-3.718943</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-33.16894475047027</v>
+        <v>-32.80770925693842</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1.778547360239164</v>
+        <v>2.324763004361072</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>30.67436577295445</v>
+        <v>30.85757047378315</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>43.54074205733119</v>
@@ -2550,7 +2550,7 @@
         <v>-16.75512158769816</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-27.60666437119737</v>
+        <v>-67.57297729938341</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -6990,46 +6990,46 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.228252</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.302037</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.301691</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.34594</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.502461</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.610519</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.288593</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.230062</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.229861</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.286609</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.269442</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.140125</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.236826</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.002077</v>
       </c>
       <c r="S100" s="3" t="n">
         <v>0</v>
@@ -7794,13 +7794,13 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.0032</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.02855</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -7809,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.246627</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -31620,7 +31620,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -37540,7 +37540,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -39836,7 +39836,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -41846,7 +41846,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -42154,7 +42158,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -44126,7 +44130,11 @@
           <t>Proceeds from disposal of property and equipment 6</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -44656,7 +44664,11 @@
           <t>Depreciation of property and equipment 8,16</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -46858,7 +46870,11 @@
           <t>Depreciation of property and equipment 8,15</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -47804,7 +47820,11 @@
           <t>Proceeds from disposal of property and equipment 8</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -48862,7 +48882,11 @@
           <t>Depreciation of property and equipment 7,14</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -48968,7 +48992,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -49908,7 +49932,11 @@
           <t>Proceeds from disposal of property and equipment 7</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -51170,7 +51198,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -53110,7 +53142,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -74646,7 +74678,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -76766,7 +76798,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -79408,7 +79440,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E671" t="inlineStr">
         <is>
           <t>-</t>
@@ -79510,7 +79546,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -82460,7 +82496,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E700" t="inlineStr">
         <is>
           <t>-</t>
@@ -82492,10 +82532,10 @@
         </is>
       </c>
       <c r="K700" s="5" t="n">
-        <v>-0.044847</v>
+        <v>0.044847</v>
       </c>
       <c r="L700" s="5" t="n">
-        <v>-0.044314</v>
+        <v>0.044314</v>
       </c>
       <c r="M700" t="inlineStr">
         <is>
@@ -82566,7 +82606,7 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -82595,13 +82635,13 @@
         </is>
       </c>
       <c r="J701" s="5" t="n">
-        <v>-0.001218</v>
+        <v>0.001218</v>
       </c>
       <c r="K701" s="5" t="n">
-        <v>-0.003447</v>
+        <v>0.003447</v>
       </c>
       <c r="L701" s="5" t="n">
-        <v>-0.00362</v>
+        <v>0.00362</v>
       </c>
       <c r="M701" t="inlineStr">
         <is>
@@ -83716,7 +83756,11 @@
           <t>Depreciation of property and equipment 8,15</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>-</t>
@@ -83743,10 +83787,10 @@
         </is>
       </c>
       <c r="J712" s="5" t="n">
-        <v>-0.041261</v>
+        <v>0.041261</v>
       </c>
       <c r="K712" s="5" t="n">
-        <v>-0.044847</v>
+        <v>0.044847</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -84980,7 +85024,11 @@
           <t>Depreciation of property and equipment 7,14</t>
         </is>
       </c>
-      <c r="D724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E724" t="inlineStr">
         <is>
           <t>-</t>
@@ -85002,10 +85050,10 @@
         </is>
       </c>
       <c r="I724" s="5" t="n">
-        <v>-0.041316</v>
+        <v>0.041316</v>
       </c>
       <c r="J724" s="5" t="n">
-        <v>-0.041261</v>
+        <v>0.041261</v>
       </c>
       <c r="K724" t="inlineStr">
         <is>
@@ -85086,7 +85134,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -85110,10 +85158,10 @@
         </is>
       </c>
       <c r="I725" s="5" t="n">
-        <v>-0.001218</v>
+        <v>0.001218</v>
       </c>
       <c r="J725" s="5" t="n">
-        <v>-0.001218</v>
+        <v>0.001218</v>
       </c>
       <c r="K725" t="inlineStr">
         <is>
@@ -86040,7 +86088,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E734" t="inlineStr">
         <is>
           <t>-</t>
@@ -86057,10 +86109,10 @@
         </is>
       </c>
       <c r="H734" s="5" t="n">
-        <v>-0.031342</v>
+        <v>0.031342</v>
       </c>
       <c r="I734" s="5" t="n">
-        <v>-0.041316</v>
+        <v>0.041316</v>
       </c>
       <c r="J734" t="inlineStr">
         <is>
@@ -86146,7 +86198,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -86165,10 +86217,10 @@
         </is>
       </c>
       <c r="H735" s="5" t="n">
-        <v>-0.001218</v>
+        <v>0.001218</v>
       </c>
       <c r="I735" s="5" t="n">
-        <v>-0.001218</v>
+        <v>0.001218</v>
       </c>
       <c r="J735" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/QST.xlsx
+++ b/output/pdf_financials_xlsx/QST.xlsx
@@ -1425,10 +1425,10 @@
         <v>10.220916</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-1.829876</v>
+        <v>-2.141811</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-3.988385</v>
+        <v>-5.236448</v>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
@@ -1496,13 +1496,13 @@
         <v>-2.792326</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>0.311935</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>1.248063</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>0.761178</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0.369914</v>
@@ -2318,10 +2318,10 @@
         <v>10.220916</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.829876</v>
+        <v>-2.141811</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.988385</v>
+        <v>-5.236448</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         <v>10.450777</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.543267</v>
+        <v>-1.855202</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.718943</v>
+        <v>-4.967006</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         <v>34.61182904617388</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-16.75512158769816</v>
+        <v>-20.14177396376699</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-67.57297729938341</v>
+        <v>-90.25020918145322</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         <v>27.31972359424537</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.56407684898434</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-23.83415246365475</v>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
@@ -3142,19 +3142,19 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.009091</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.379105</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.020771</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.012542</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -3205,19 +3205,19 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.852578</v>
+        <v>2.861669</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>2.304478</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2.863257</v>
+        <v>3.242362</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>3.044999</v>
+        <v>3.06577</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.148171</v>
+        <v>2.160713</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>1.055393</v>
@@ -3646,19 +3646,19 @@
         <v>6290.701</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.169637</v>
+        <v>0.160546</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.113536</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.202012</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.168865</v>
+        <v>0.148094</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.7747309999999999</v>
+        <v>0.762189</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.6972660000000001</v>
@@ -4696,19 +4696,19 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.883389</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.676806</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.545912</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.804438</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4885,19 +4885,19 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.17902</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.21194</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.488787</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.6115119999999999</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0835</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -4948,19 +4948,19 @@
         <v>0</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>1.062409</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.888746</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.488787</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>1.157424</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.887938</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0</v>
@@ -5098,25 +5098,25 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.273266</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.111032</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.223051</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.27949</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.192845</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.150643</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>0.207706</v>
       </c>
     </row>
     <row r="71">
@@ -5161,25 +5161,25 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.273266</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.111032</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.223051</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.27949</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.192845</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.150643</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>0.207706</v>
       </c>
     </row>
     <row r="72">
@@ -5389,19 +5389,19 @@
         <v>1230.052</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1.547603</v>
+        <v>0.485194</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.095088</v>
+        <v>0.206342</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.689143</v>
+        <v>2.200356</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.632534</v>
+        <v>0.47511</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1.100782</v>
+        <v>0.212844</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>1.580571</v>
@@ -5413,25 +5413,25 @@
         <v>2.216312</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>3.096328</v>
+        <v>2.823062</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>1.153085</v>
+        <v>1.042053</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>1.300677</v>
+        <v>1.077626</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>2.519004</v>
+        <v>2.239514</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.425847</v>
+        <v>2.233002</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>2.038676</v>
+        <v>1.888033</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>1.925287</v>
+        <v>1.717581</v>
       </c>
     </row>
     <row r="76">
@@ -5602,25 +5602,25 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.526891</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.33534</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.400544</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>0.257398</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>0.063385</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>0.789726</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>0</v>
+        <v>0.642254</v>
       </c>
     </row>
     <row r="79">
@@ -5665,25 +5665,25 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.526891</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.33534</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.400544</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>0</v>
+        <v>0.257398</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>0</v>
+        <v>0.063385</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>0</v>
+        <v>0.789726</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>0</v>
+        <v>0.642254</v>
       </c>
     </row>
     <row r="80">
@@ -5747,40 +5747,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.02264573897750267</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.01313279845597559</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.02045775680472734</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.01838985780612622</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.01051948685365896</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.04454597889652316</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>0.04310581789582182</v>
       </c>
     </row>
     <row r="81">
@@ -6077,25 +6063,25 @@
         <v>0.258233</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.526891</v>
+        <v>0</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>1.301527</v>
+        <v>0.966187</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>1.275808</v>
+        <v>0.875264</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0.81782</v>
+        <v>0.560422</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>0.332321</v>
+        <v>0.268936</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>0.789726</v>
+        <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>0.642254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -8436,10 +8422,10 @@
         <v>0</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-0.323202</v>
       </c>
       <c r="S121" s="3" t="n">
-        <v>0</v>
+        <v>-0.021969</v>
       </c>
     </row>
     <row r="122">
@@ -9029,10 +9015,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>3.995669</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>2.166301</v>
@@ -9044,17 +9028,13 @@
         <v>7.323303</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>5.82141</v>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.64057</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>5.127371</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>6.733897</v>
       </c>
       <c r="L130" s="3" t="n">
         <v>3.847862</v>
@@ -9062,13 +9042,11 @@
       <c r="M130" s="3" t="n">
         <v>8.809644</v>
       </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N130" s="3" t="n">
+        <v>13.491383</v>
       </c>
       <c r="O130" s="3" t="n">
-        <v>16.304224</v>
+        <v>16.307029</v>
       </c>
       <c r="P130" s="3" t="n">
         <v>14.66008</v>
@@ -9238,10 +9216,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>2.166301</v>
       </c>
       <c r="F133" s="3" t="n">
         <v>4.405624</v>
@@ -9255,15 +9231,11 @@
       <c r="I133" s="3" t="n">
         <v>5.127371</v>
       </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J133" s="3" t="n">
+        <v>6.733897</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>3.847863</v>
       </c>
       <c r="L133" s="3" t="n">
         <v>8.809644</v>
@@ -9271,10 +9243,8 @@
       <c r="M133" s="3" t="n">
         <v>13.491383</v>
       </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N133" s="3" t="n">
+        <v>16.307029</v>
       </c>
       <c r="O133" s="3" t="n">
         <v>14.66008</v>
@@ -11026,7 +10996,11 @@
           <t>Current portion of lease obligations 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11504,7 +11478,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -15786,7 +15764,11 @@
           <t>Current portion of lease obligations 13</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -16000,7 +15982,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -33572,7 +33558,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -37226,7 +37216,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -39216,7 +39210,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -39312,7 +39310,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -42570,7 +42572,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -43194,7 +43200,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -43612,7 +43622,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -44026,7 +44040,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -46248,7 +46266,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -47506,7 +47528,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -49828,7 +49854,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -51726,7 +51756,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -52258,7 +52292,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -52362,7 +52400,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -62936,7 +62978,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -75100,7 +75146,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>-</t>
